--- a/markets/fashion/Kuwait_Fashion_Stores.xlsx
+++ b/markets/fashion/Kuwait_Fashion_Stores.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fashion Stores" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed - platform subdomain" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26660,7 +26661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27003,7 +27004,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -27013,6 +27013,94 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>Removed 2 rows from Fashion Stores (now 116); each is listed in the Excluded sheet with source "Deliverable cleanup (fashion-stores package)". Website values normalised to clean storefront URLs (2 changed). Counts above (total, type, gender, platform, size tier, verification status) reflect the cleaned list; any by-source/by-channel/signal-origin/QA breakdowns are as at the original run (pre-cleanup). Note: the Boutiqaat judgment call described above was resolved by removing it (beauty-led hybrid marketplace).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Root-domain cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Rows before</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kept as-is</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Replaced with root domain</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Removed (no own domain / duplicate of root)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Rows after</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Store Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Old URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>

--- a/markets/fashion/Kuwait_Fashion_Stores.xlsx
+++ b/markets/fashion/Kuwait_Fashion_Stores.xlsx
@@ -52,12 +52,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,19 +424,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,40 +455,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Website Pages Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Count Method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Count Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Size Tier (best-effort)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Evidence URL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Classification Signal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Discovery Source</t>
         </is>
@@ -501,42 +520,55 @@
           <t>https://abatiboutique.online/</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>https://abatiboutique.online/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abaya, عباية, قميص, ملابس</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -553,42 +585,55 @@
           <t>https://abayalabkw.com/</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>https://abayalabkw.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abaya, بشت, بنطلون, تنورة, جاكيت, عبايات</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -605,42 +650,55 @@
           <t>https://abreezabaya.com/ar</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>https://abreezabaya.com/</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>homepage nav: abayas</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -657,42 +715,53 @@
           <t>https://www.adidas.com.kw/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>https://www.adidas.com.kw/</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -709,42 +778,55 @@
           <t>https://en-kw.aivi.com/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>16312869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>https://en-kw.aivi.com/</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">homepage nav: </t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -761,42 +843,55 @@
           <t>https://alaseel.com.kw/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="n">
+        <v>775</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>https://alaseel.com.kw/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: بناطيل, بيجامات, جاكيت, دراعة, فساتين, فستان</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -813,42 +908,55 @@
           <t>https://alnasser.net/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="n">
+        <v>21789</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>https://alnasser.net/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>homepage nav: apparel, blouse, cardigan, dress, hoodies, jacket</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -865,42 +973,55 @@
           <t>https://alwareefkw.com/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="n">
+        <v>1332</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>https://alwareefkw.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: عبايه</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -917,42 +1038,55 @@
           <t>https://www.alhazeemfashion.com.kw/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>https://www.alhazeemfashion.com.kw/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>homepage nav: fashion, shemagh</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -969,42 +1103,55 @@
           <t>https://abayaislamiya.com/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>https://abayaislamiya.com/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1021,42 +1168,55 @@
           <t>https://almohrastyle.com/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>https://almohrastyle.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: blouse, pants, عبايات</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1073,42 +1233,55 @@
           <t>https://www.aloyoga.com/en-kw</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="n">
+        <v>1316858</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>https://www.aloyoga.com/en-kw</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1125,42 +1298,55 @@
           <t>https://ambroseabayas.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Verified - live re-check (KWD prices / cart on Kuwait storefront)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>https://ambroseabayas.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abaya, abayas, blazer, modest</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1177,42 +1363,53 @@
           <t>https://www.americaneagle.com.kw/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250330043324/https://www.americaneagle.com.kw/en/buy-ae-ruffle-shirt-midi-dress-green.html</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1229,42 +1426,55 @@
           <t>https://arashastore.com/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="n">
+        <v>377</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Zid</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>https://arashastore.com/</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>homepage nav: ازياء, بلوزة, تنورة, جلابيات, جلابية, طقم</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1281,42 +1491,55 @@
           <t>https://athleta.com.kw/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>1561</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>https://athleta.com.kw/</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>homepage nav: clothing, dresses, hoodies, jackets, jumpsuits, leggings</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1333,42 +1556,55 @@
           <t>https://aysunkw.com/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>https://aysunkw.com/</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>homepage nav: coats, pants, shirt, shirts</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1385,42 +1621,55 @@
           <t>https://b2lglam.com/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>https://b2lglam.com/</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>homepage nav: عبايتج</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1437,42 +1686,55 @@
           <t>https://www.balenciaga.com/en-kw</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sitemap (KW pages only)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>https://www.balenciaga.com/en-kw</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1489,42 +1751,55 @@
           <t>https://www.bananarepublic.com.kw/</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="n">
+        <v>1349</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>https://www.bananarepublic.com.kw/</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>homepage nav: blazer, blazers, blouses, clothing, coats, denim</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1541,42 +1816,53 @@
           <t>https://www.bershka.com/kw/</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>https://www.bershka.com/kw/ar/%D9%86%D8%B3%D8%A7%D8%A1/shoes-c1010838068.html</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1593,42 +1879,55 @@
           <t>https://kw.p3ly.com/</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="n">
+        <v>421</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>https://kw.p3ly.com/</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>homepage nav: أزياء, لانجري, ملابس</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1645,42 +1944,55 @@
           <t>https://www.blackwhitekw.com/</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="n">
+        <v>1489</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>https://www.blackwhitekw.com/</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>homepage nav: بناطيل, طقم, فساتين, قمصان, ملابس</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1697,42 +2009,55 @@
           <t>https://www.blinktrends.com.kw/</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="n">
+        <v>7519</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>https://www.blinktrends.com.kw/</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1749,42 +2074,55 @@
           <t>https://bloomingdales.com.kw/</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v>142119</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>https://bloomingdales.com.kw/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>homepage nav: أزياء</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1801,42 +2139,55 @@
           <t>https://bluestoreq8.com/</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>https://bluestoreq8.com/</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>homepage nav: أزياء</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1853,42 +2204,55 @@
           <t>https://www.bottegaveneta.com/en-kw</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sitemap (KW pages only)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>https://www.bottegaveneta.com/en-kw</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1905,42 +2269,55 @@
           <t>https://www.brandsforless.com/en-kw</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="n">
+        <v>39815</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>https://www.brandsforless.com/en-kw</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1957,42 +2334,55 @@
           <t>https://kw.burberry.com/</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="n">
+        <v>3896</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Verified - live re-check (KWD prices / cart on Kuwait storefront)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>https://kw.burberry.com/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>homepage nav: activewear, blazers, clothes, coats, denim, dresses</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2009,42 +2399,53 @@
           <t>https://cabanakw.com/</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Not available (no sitemap found; no sitemap/shop total/platform count and no archive captures)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>https://cabanakw.com/</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>homepage nav: dresses, polo shirts, shirts, shorts, skirts, swimwear</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2061,42 +2462,53 @@
           <t>https://www.calvinklein.com.kw/</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>https://www.calvinklein.com.kw/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2113,42 +2525,55 @@
           <t>https://www.centrepointstores.com/kw/en/</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="n">
+        <v>65605</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20261011132057/https://www.centrepointstores.com/sa/ar/buy-amla-baby-remote-control-swing-system-car/p/169778248?gbraid=0AAAAACwAzs3EdPrFuSSMNm0l0Slgun4BB&amp;gad_source=5&amp;gad_campaignid=22918204761&amp;gclid=EAIaIQobChMI8P_4gYaylwMVYsdPCB0syjznEAEYASABEgIwC_D_BwE</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2165,42 +2590,55 @@
           <t>https://chickuwait.com/</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="n">
+        <v>377</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>https://chickuwait.com/</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2217,42 +2655,55 @@
           <t>https://kw.cos.com/en/</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="n">
+        <v>3588</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>https://kw.cos.com/en/</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>homepage nav: clothing, fashion</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2269,42 +2720,55 @@
           <t>https://darraferoz.com/</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>https://darraferoz.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abayas, activewear, dress, dresses</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2321,42 +2785,55 @@
           <t>https://decathlon.com.kw/</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="n">
+        <v>2603</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>https://decathlon.com.kw/</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>directory category 'Sports, Fitness &amp; Outdoor' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2373,42 +2850,55 @@
           <t>https://www.desigual.com/en_KW/</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="n">
+        <v>6220</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>https://www.desigual.com/en_KW/</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>directory category 'Pets' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2425,42 +2915,55 @@
           <t>https://kw.diesel.com/</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>https://kw.diesel.com/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2477,42 +2980,55 @@
           <t>https://dkny.com.kw/</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251012213912/https://dkny.com.kw/ar/collections/fp-shoes/products/kw356902blk</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2529,42 +3045,55 @@
           <t>https://www.dolcegabbana.com/en-kw/</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sitemap (KW pages only)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Verified - live re-check (KWD prices / cart on Kuwait storefront)</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>https://www.dolcegabbana.com/en-kw/</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Kuwait-locale storefront (/en-kw, KWD) with clothing nav; homepage nav fetched during locale probe</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2581,42 +3110,55 @@
           <t>https://elitewholesalekuwait.com/</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>https://elitewholesalekuwait.com/</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>homepage nav: abaya</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2633,42 +3175,55 @@
           <t>https://ar-kw.emvano.com/</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="n">
+        <v>76156</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>https://ar-kw.emvano.com/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>homepage nav: بناطيل, فساتين, قمصان, ملابس</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2685,42 +3240,55 @@
           <t>https://www.etedalalhmaidi.com/kw</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>https://www.etedalalhmaidi.com/kw/</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>directory category 'Flowers, Gifts &amp; Party' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2737,42 +3305,55 @@
           <t>https://falke.com.kw/</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="n">
+        <v>2385</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260422015803/https://falke.com.kw/products/men-long-sleeve-shirt-maximum-warm-33523_7385</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2789,42 +3370,53 @@
           <t>https://www.footlocker.com.kw/</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>https://www.footlocker.com.kw/en/</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">homepage nav: </t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2841,42 +3433,55 @@
           <t>https://gant.com.kw/</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>https://gant.com.kw/</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2893,42 +3498,55 @@
           <t>https://www.gap.com.kw/</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="n">
+        <v>2388</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>https://www.gap.com.kw/</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>homepage nav: clothing, denim, dress, dresses, hoodie, jacket</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2945,42 +3563,55 @@
           <t>https://www.giordano.com.kw/ar</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="n">
+        <v>413</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>https://www.giordano.com.kw/</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2997,42 +3628,55 @@
           <t>https://www.gymshark.com.kw/</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="n">
+        <v>11563</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>https://www.gymshark.com.kw/</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>homepage nav: بناطيل, ملابس</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3049,42 +3693,53 @@
           <t>https://kw.hm.com/</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>https://kw.hm.com/ar/buy-2-pack-make-sponges-pink-purple</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3101,42 +3756,53 @@
           <t>https://www.harveynichols.com.kw/en/</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>https://www.harveynichols.com.kw/en/</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>homepage nav: fashion</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3153,42 +3819,55 @@
           <t>https://hawraaabaya.com/</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="n">
+        <v>1142</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Zid</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>https://hawraaabaya.com/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>homepage nav: تنورة, حجاب, طقم, عبايات</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3205,42 +3884,53 @@
           <t>https://www.hugoboss.com/kw/</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="n"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260211012338/https://www.hugoboss.com/kw/en/cotton-jersey-t-shirt-with-stripe-and-logo/4063548594390.html</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3257,42 +3947,55 @@
           <t>https://www.intersport.com.kw/</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="n">
+        <v>20223</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>https://www.intersport.com.kw/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>homepage nav: clothing, hoodies, jackets, swimwear, underwear</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3309,42 +4012,55 @@
           <t>https://justladykw.com/</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>https://justladykw.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: فساتين</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3361,42 +4077,55 @@
           <t>https://kiabi.kw/</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="n">
+        <v>1464</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>https://kiabi.kw/</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3413,42 +4142,55 @@
           <t>https://ku-market.com/</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="n">
+        <v>698</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>https://ku-market.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: activewear, blouses, clothing, coats, dresses, jackets</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3465,42 +4207,55 @@
           <t>https://www.kuwaitboutique.com/</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="3" t="n">
+        <v>631</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>https://www.kuwaitboutique.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: clothes, hoodie, hoodies</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3517,42 +4272,53 @@
           <t>https://www.lasenzakuwait.com/</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>https://www.lasenzakuwait.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: lingerie, pants, shorts, underwear</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3569,42 +4335,55 @@
           <t>https://lab.com.kw/</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>https://lab.com.kw/</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3621,42 +4400,53 @@
           <t>https://www.lacoste.com.kw/</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>https://www.lacoste.ae/</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>homepage nav: clothing, coats, dresses, fashion, jackets, loungewear</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3673,42 +4463,53 @@
           <t>https://www.lcwaikiki.com.kw/</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="n"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>https://www.lcwaikiki.com.kw/</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3725,42 +4526,53 @@
           <t>https://www.lifestyleshops.com/kw/en</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>https://www.lifestyleshops.com/kw/en</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3777,42 +4589,55 @@
           <t>https://listroma.com/</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>https://listroma.com/</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>homepage nav: أزياء</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3829,42 +4654,53 @@
           <t>https://gcc.luluhypermarket.com/en-kw/</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ConnectionError: HTTPConnectionPool(host='www.gcc.luluhypermarket.com', port=80): Max retries exc))</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20261004041456/https://gcc.luluhypermarket.com/en-kw/bee-polypropylene-lunch-box-with-spoon-fork-set-782/p/2433012/</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3881,42 +4717,55 @@
           <t>https://lulwamoda.com/</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="n">
+        <v>484</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>https://lulwamoda.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: عبايات</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3933,42 +4782,55 @@
           <t>https://www.maje.com.kw/</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="3" t="n">
+        <v>1757</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>https://www.maje.com.kw/</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>homepage nav: blazers, cardigan, cardigans, denim, dress, dresses</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3985,42 +4847,53 @@
           <t>https://shop.mango.com/kw/</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 429 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>https://shop.mango.com/kw/en/p/kids/baby-girls/sweatshirts/hello-kitty-sweatshirt/37073306/43/00</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4037,42 +4910,55 @@
           <t>https://www.marksandspencer.com.kw/</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="n">
+        <v>8019</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>https://www.marksandspencer.com.kw/en/fashion</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>homepage nav: fashion, jackets, lingerie, nightwear, shirts, skirts</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4089,42 +4975,53 @@
           <t>https://www.massimodutti.com/kw/</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>https://www.massimodutti.com/kw/runway/runway-fw25-w</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4141,42 +5038,53 @@
           <t>https://www.maxfashion.com/kw/</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251022035748/https://www.maxfashion.com/kw/ar/buy-beaded-layered-necklace-with-lobster-clasp-closure/p/165457961</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4193,42 +5101,55 @@
           <t>https://melissia.com.kw/ar/</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>https://melissia.com.kw/ar/</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>homepage nav: abaya</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4245,42 +5166,55 @@
           <t>https://www.michaelkors.com.kw/</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>SFCC</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>https://www.michaelkors.com.kw/</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>homepage nav: clothing, dresses, jackets</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4297,42 +5231,53 @@
           <t>https://www.miumiu.com/kw/ar.html</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="n"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ReadTimeout: HTTPConnectionPool(host='www.miumiu.com', port=80): Read timed out. (read timeou))</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>https://www.miumiu.com/kw/</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4349,42 +5294,55 @@
           <t>https://modish.com.kw/</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="n">
+        <v>1977</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>https://modish.com.kw/</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>homepage nav: blazers, cardigans, coats, denim, dresses, hijab</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4401,42 +5359,53 @@
           <t>https://www.moncler.com/en-kw/</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>https://www.moncler.com/en-kw/</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4453,42 +5422,55 @@
           <t>https://mrmr.com.kw/</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>https://mrmr.com.kw/</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>homepage nav: fashion, دراعة, فستان</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4505,42 +5487,53 @@
           <t>https://www.namshi.com/kuwait-ar/</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ReadTimeout: HTTPConnectionPool(host='www.namshi.com', port=80): Read timed out. (read timeou))</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>https://www.namshi.com/kuwait-ar/buy-ecotools-360-ultimate-sheer-foundation-brush/ZCCFCFFE879C5D3A8C0D0Z/p/</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4557,42 +5550,55 @@
           <t>https://nayra.style/ar</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>https://nayra.style/</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4609,42 +5615,55 @@
           <t>https://www.newbalance.com.kw/en/</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="n">
+        <v>2295</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>https://www.newbalance.com.kw/en/</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">homepage nav: </t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4661,42 +5680,53 @@
           <t>https://www.nextdirect.com/kw/ar</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>https://www.nextdirect.com/kw/</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4713,42 +5743,55 @@
           <t>https://www.nike.com.kw/en/</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="n">
+        <v>22212</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>https://www.nike.com.kw/en/home/</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>homepage nav: clothing, hoodies, jackets, shorts, sportswear, sweatshirts</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4765,42 +5808,55 @@
           <t>https://oosha.store/</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>https://oosha.store/</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>homepage nav: jacket</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4817,42 +5873,55 @@
           <t>https://kuwait.ounass.com/</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="3" t="n">
+        <v>393961</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>https://kuwait.ounass.com/</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>homepage nav: clothing</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4869,42 +5938,53 @@
           <t>https://www.oysho.com/kw/</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="n"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>https://www.oysho.com/kw/%D8%A7%D9%95%D8%B7%D9%84%D8%A7%D9%84%D8%A9-%D9%83%D8%A7%D9%85%D9%84%D8%A9-compressive-%D8%B4%D9%88%D8%B1%D8%AA-%D8%B3%D9%88%D8%AF%D8%A7%D8%A1-l30349206800BSBS</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4921,42 +6001,53 @@
           <t>https://www.prada.com/kw/ar.html</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ReadTimeout: HTTPConnectionPool(host='www.prada.com', port=80): Read timed out. (read timeout))</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>https://www.prada.com/kw/</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4973,42 +6064,53 @@
           <t>https://www.pullandbear.com/kw/</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>https://www.pullandbear.com/kw/%D8%AC%D9%8A%D9%86%D8%B2-%D9%81%D8%B6%D9%81%D8%A7%D8%B6-%D8%A8%D9%82%D8%B5%D8%A9-%D8%A8%D8%A7%D9%84%D9%88%D9%86-%D9%88%D8%A8%D9%84%D9%8A%D8%B3%D9%8A%D9%87-l07662409</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5025,42 +6127,55 @@
           <t>https://www.rivafashion.com/en-kw/</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="3" t="n">
+        <v>74598</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>https://www.rivafashion.com/en-kw/</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5077,42 +6192,55 @@
           <t>https://sstylekw.com/</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>https://sstylekw.com/</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>homepage nav: dress, ready to wear</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -5129,42 +6257,55 @@
           <t>https://www.sandro.com.kw/</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="n">
+        <v>2247</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251018070132/https://www.sandro.com.kw/ar/products/sface00434-slim-leather-belt-brown</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5181,42 +6322,55 @@
           <t>https://shadow.com.kw/</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="3" t="n">
+        <v>557</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>https://shadow.com.kw/</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>homepage nav: abaya, abayas, blazer</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5233,42 +6387,53 @@
           <t>https://ar.shein.com/</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="n"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ConnectionError: HTTPConnectionPool(host='www.ar.shein.com', port=80): Max retries exceeded with ))</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>https://us.shein.com/?cdn_rsite=cf&amp;ref=www&amp;rep=dir&amp;ret=us</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>homepage nav: clothing, fashion</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5285,42 +6450,55 @@
           <t>https://sj-abaya.com/ar-kw/</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>https://sj-abaya.com/ar-kw/</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5337,42 +6515,55 @@
           <t>https://sleepwearkuwait.com/</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="3" t="n">
+        <v>1597</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>https://sleepwearkuwait.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: dress, loungewear, pajama, shirts</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5389,42 +6580,55 @@
           <t>https://www.snkr.com.kw/</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="3" t="n">
+        <v>11634</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>https://www.snkr.com.kw/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>homepage nav: apparel</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5441,42 +6645,55 @@
           <t>https://souqsara.com.kw/</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="3" t="n">
+        <v>391</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>https://souqsara.com.kw/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: بنطلون, تنورة, جاكيت, حجاب, طقم, عباية</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5493,42 +6710,55 @@
           <t>https://specialabayakw.com/</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>https://specialabayakw.com/</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5545,42 +6775,53 @@
           <t>https://www.splashfashions.com/kw/</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="n"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250524064006/https://www.splashfashions.com/kw/ar/%D8%A7%D9%83%D8%B3%D8%B3%D9%88%D8%A7%D8%B1%D8%A7%D8%AA/%D8%A7%D9%84%D9%86%D8%B3%D8%A7%D8%A1/%D8%AD%D9%82%D8%A7%D8%A6%D8%A8-%D9%8A%D8%AF-%D9%86%D8%B3%D8%A7%D8%A6%D9%8A%D8%A9/%D8%B4%D9%88%D9%85%D8%A7%D8%B1%D8%AA-%D8%B4%D9%86%D8%B7%D8%A9-%D8%AA%D9%88%D8%AA-%D9%83%D8%AA%D9%84-%D9%85%D9%84%D9%88%D9%91%D9%86%D8%A9-%D9%88%D8%B3%D8%AD%D9%91%D8%A7%D8%A8-%D8%A5%D8%BA%D9%84%D8%A7%D9%82-%D9%88%D9%85%D9%82%D8%A8%D8%B6-%D9%85%D8%B2%D8%AF%D9%88%D8%AC-%D9%85%D9%86-%D9%85%D9%8A%D8%B3%D9%8A/p/c/cpwomen</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5597,42 +6838,55 @@
           <t>https://squatwolf.com/en-kw/</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>sitemap (KW pages only)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>https://squatwolf.com/en-kw/products/qtr-zip-untamed-top-surf-spray-print</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5649,42 +6903,53 @@
           <t>https://www.stradivarius.com/kw/en/</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="3" t="n"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>https://www.stradivarius.com/kw/en/</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -5701,42 +6966,55 @@
           <t>https://stylishop.com/kw/en</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="n">
+        <v>247204</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>https://stylishop.com/kw/en</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -5753,42 +7031,55 @@
           <t>https://en-kw.sssports.com/</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="3" t="n">
+        <v>30512</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>https://en-kw.sssports.com/</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>homepage nav: clothing, dresses, hijab, hoodies, jackets, leggings</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5805,42 +7096,55 @@
           <t>https://www.tedbaker.kw/</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="3" t="n">
+        <v>2787</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>https://www.tedbaker.kw/</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5857,42 +7161,55 @@
           <t>https://www.theathletesfoot.com.kw/</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="3" t="n">
+        <v>20647</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>https://www.theathletesfoot.com.kw/</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>homepage nav: apparel, dresses, hoodies, jackets, leggings, pants</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5909,42 +7226,55 @@
           <t>https://theonekdshop.com/</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="3" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>https://theonekdshop.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: activewear, blazers, cardigans, clothes, clothing, dresses</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5961,42 +7291,55 @@
           <t>https://thoubi.com/</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="3" t="n">
+        <v>3135</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>https://thoubi.com/</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Men' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -6013,42 +7356,55 @@
           <t>https://www.toryburch.com.kw/</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="3" t="n">
+        <v>1416</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>https://www.toryburch.com.kw/</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>homepage nav: clothing, denim, فساتين, قفطان, قمصان, ملابس</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6065,42 +7421,55 @@
           <t>https://triumph.com.kw/</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="3" t="n">
+        <v>421</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251111021404/https://triumph.com.kw/ar/collections/sloggi_women_knickers_string-thongs/products/10214636-6308</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6117,42 +7486,55 @@
           <t>https://www.uspoloassn.com.kw/</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="3" t="n">
+        <v>2307</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>https://www.uspoloassn.com.kw/</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6169,42 +7551,55 @@
           <t>https://www.valentino.com/en-kw/</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="3" t="n">
+        <v>2357</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>sitemap (KW pages only)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712150340/https://www.valentino.com/en-kw/men/shoes/loafers-and-driver?pagination=2</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6221,42 +7616,53 @@
           <t>https://www.versace.com/kw/en/</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="3" t="n"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>https://www.versace.com/kw/en/</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -6273,42 +7679,55 @@
           <t>https://www.victoriassecret.com.kw/</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="3" t="n">
+        <v>21913</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>https://www.victoriassecret.com.kw/en/</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>homepage nav: lingerie</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6325,42 +7744,55 @@
           <t>https://www.vogacloset.com/kw</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="3" t="n">
+        <v>738413</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>https://www.vogacloset.com/kw</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -6377,42 +7809,55 @@
           <t>https://wsfabaya.com/</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>https://wsfabaya.com/</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>homepage nav: abaya, abayas, blazers, dress, fashion, modest</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6429,42 +7874,55 @@
           <t>https://wynwoodkw.com/</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>https://wynwoodkw.com/</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>homepage nav: hoodies, shirts, shorts, tshirts</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -6481,42 +7939,53 @@
           <t>https://www.zara.com/kw/</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="3" t="n"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>https://www.zara.com/kw/ar/monsters-l18726.html</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -26661,7 +28130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27004,6 +28473,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -27016,6 +28486,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -27073,7 +28544,168 @@
         <v>116</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Page count</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Rows counted (of 116)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Counted by method</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Size distribution (pages per site)</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1-50</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>51-200</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>201-1,000</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1,001-5,000</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5,001-20,000</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20,001-100,000</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>&gt;100,000</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0 (market segment empty)</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" ht="95" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A58:C58"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/markets/fashion/Kuwait_Fashion_Stores.xlsx
+++ b/markets/fashion/Kuwait_Fashion_Stores.xlsx
@@ -1687,11 +1687,11 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>22704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sitemap (KW pages only)</t>
+          <t>sitemap (partial: 27 of 28 sitemap files read)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2205,11 +2205,11 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>16424</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>sitemap (KW pages only)</t>
+          <t>sitemap (partial: 85 of 86 sitemap files read)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3046,11 +3046,11 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0</v>
+        <v>512564</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sitemap (KW pages only)</t>
+          <t>sitemap (whole site, no market segment)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sitemap</t>
+          <t>sitemap (partial: 5 of 9 sitemap files read)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -28580,7 +28580,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45">
@@ -28596,89 +28596,89 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>sitemap (partial: some child sitemaps unreadable)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sitemap (whole site, no market segment)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B48" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>Size distribution (pages per site)</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>Rows</t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1-50</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>51-200</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>201-1,000</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1,001-5,000</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5,001-20,000</t>
+          <t>201-1,000</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20,001-100,000</t>
+          <t>1,001-5,000</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>&gt;100,000</t>
+          <t>5,001-20,000</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -28688,23 +28688,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0 (market segment empty)</t>
+          <t>20,001-100,000</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" ht="95" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank.</t>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>&gt;100,000</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" ht="150" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A59:C59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markets/fashion/Kuwait_Fashion_Stores.xlsx
+++ b/markets/fashion/Kuwait_Fashion_Stores.xlsx
@@ -4654,10 +4654,12 @@
           <t>https://gcc.luluhypermarket.com/en-kw/</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>6839</v>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Not available (unreachable (ConnectionError: HTTPConnectionPool(host='www.gcc.luluhypermarket.com', port=80): Max retries exc))</t>
+          <t>archive</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -28558,7 +28560,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
@@ -28590,7 +28592,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -28620,7 +28622,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
@@ -28682,7 +28684,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">

--- a/markets/fashion/Kuwait_Fashion_Stores.xlsx
+++ b/markets/fashion/Kuwait_Fashion_Stores.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7993,6 +7993,526 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Leia</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://activeleia.com/</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>233</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://activeleia.com/products/zipper-jacket-set</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Aidan Global</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://aidanglobal.com/</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>796</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>WooCommerce</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://aidanglobal.com/product/premium-racefit-cycling-jersey-corex/</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Aurellia Official</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://aurelliaofficial.com/</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>10</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://aurelliaofficial.com/products/caramel-sweater-dark-chocolate-leather-skirt</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Black Line</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://blacklinewear.com/</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>73</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>OpenCart</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://blacklinewear.com/</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://doekw.com/</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Women, Men</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Not detected</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://doekw.com/en/products/4/men-clothing</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Hamem Design</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://hamemdesign.com/</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>142</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://hamemdesign.com/products/عباة-ميلا-بني-أو-أسود</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Maisonr</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://maisonrkw.com/</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>35</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Small / local brand</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://maisonrkw.com/</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ShopFlain</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://shopflain.com/</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>17039</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>nopCommerce</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://shopflain.com/pants-3</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8004,7 +8524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D914"/>
+  <dimension ref="A1:D967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -28118,6 +28638,1172 @@
       <c r="D914" t="inlineStr">
         <is>
           <t>Deliverable cleanup (fashion-stores package)</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>3DPRINT</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>https://www.3dprintkw.com/</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>53Sports &amp; Fitness</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>https://53sports.com/</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>albairaqkw</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>https://www.albairaqkw.com/</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>albayrouni Pharmacy</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>https://albayrouni-pharmacy.com.kw/</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>All Drops Store</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>https://www.alldrops.store/</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Alsultan Pharmacy</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>https://www.alsultanpharmacy.com/</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Althenayan Honey</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>http://althenayanhoney.com/</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Anesthesia Contact Lenses</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>http://anesthesialenses.com/</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>ArabiaScents</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>https://arabiascents.com/</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>أريج الكويت للعطور</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>https://areejkw.com/</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>أطيب الدولية</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>https://atiabintl.com/</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Beautica Cosmetics</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>https://www.beautica-cosmetics.com/</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Bella Contact Lenses</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>https://bellacontactlenses.com/</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>BLOCK7.STORE</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>https://block7.store/</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>BoardGames Q8</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>https://boardgamesq8.com/</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>By Talal</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>https://bytalal.com/</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Carmen Professional</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>https://carmenprofessional.com/</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>eBaqala.com</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>https://ebaqala.com/</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>FAWAAH</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>https://fawaah.com/</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Findik Nuts</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>https://findiknuts.com/</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>fnbyfn</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>https://fnbyfn.com/</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>فريسيا</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>https://freesia-beauty.com/</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>GAMESQ8.com</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>https://gamesq8.com/</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Ginza Market Kuwait</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>https://www.ginzamartkw.com/</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Henzadem</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>https://henzadem.com/</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>H&amp;S Store</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>https://hsstore.com/</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>آي سيلكت</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>https://iselectkw.com/</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Kent Web Store Kuwait</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>https://kentwebstore.com/</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Kuwait Diet</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>https://kuwait-diet.com/</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Loroyal Color contact</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>https://loroyallenses.com/</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>مزهاف</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>https://mzhaf.com/</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Noor Foods KW</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>https://noororganicfood.com/</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Noor Organic Q8</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>https://noororganicq8.com/</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>PERFUME KUWAIT</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>https://otorkuwit.com/</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Perfumes600</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>https://perfumes600.com/</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Pharmazone</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>https://pharmazone.com/</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Puchi Box</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>https://puchi-kw.com/</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>REGAL HONEY</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>https://regal-honey.com/</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Sedra</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>https://sedrahoney.com/</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Sedra Perfumes</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>https://www.sedraperfumes.com/</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Sincerely Jules</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>https://sincerelyjuleskw.com/</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Smart Collection</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>https://smartcollectionkw.com/</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Smart Hydro</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>https://smarthydro.net/</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>ستايلاتي</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>https://stylati.com/</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Telefonati</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>https://www.telefonati.com/</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>The Honey Garden</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>https://thehoneygarden.com/</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>The Shop Wings</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>https://theshopwings.com/</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Trust Pharmacy</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>https://thetrustpharmacy.com/</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Tula Aloud</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>https://tula-aloud.com/</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>tum.tum.tam</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>https://www.tumtumtam.com/</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Twenty Five</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>https://twentyfive.com.kw/</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>ugreenkuwait</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>https://ugreenkuwait.com/</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>ZwarahHome</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>https://zwarahhome.com/</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
         </is>
       </c>
     </row>
@@ -28132,7 +29818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -28171,7 +29857,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -28546,89 +30232,100 @@
         <v>116</v>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Page count</t>
+          <t>StoreLeads gap fill</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rows counted (of 116)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>88</v>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill of the Kuwait directory (see directory workbook, sheet 'Research Coverage')</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gap stores added to the directory</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>Counted by method</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>Rows</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Gap stores added to the fashion list</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sitemap</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>74</v>
+          <t>Gap stores not fashion (listed in Excluded)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>archive</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>sitemap (partial: some child sitemaps unreadable)</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-    </row>
+          <t>Fashion rules</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Adult clothing (women, men, unisex) as a fashion-only store or a clothing section; abaya/thobe/modest wear, lingerie and sportswear count; kids-only and shoes/bags/accessories-only do not. Classified from homepage nav/meta and product pages (EN+AR keywords), reviewed manually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sitemap (whole site, no market segment)</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Page count</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>28</v>
-      </c>
-    </row>
+          <t>Rows counted (of 124)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Size distribution (pages per site)</t>
+          <t>Counted by method</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
@@ -28640,75 +30337,162 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1-50</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>9</v>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>51-200</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>9</v>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>201-1,000</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>17</v>
+          <t>sitemap (partial: some child sitemaps unreadable)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1,001-5,000</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>28</v>
+          <t>sitemap (whole site, no market segment)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>Size distribution (pages per site)</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1-50</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>51-200</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>201-1,000</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1,001-5,000</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>5,001-20,000</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>20,001-100,000</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>&gt;100,000</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" ht="150" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="150" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
         </is>
@@ -28716,7 +30500,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A66:C66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markets/fashion/Kuwait_Fashion_Stores.xlsx
+++ b/markets/fashion/Kuwait_Fashion_Stores.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -432,14 +432,18 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,40 +474,60 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Organic Traffic (KW, Semrush)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Organic Keywords (KW)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Traffic Check Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Traffic Note</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Size Tier (best-effort)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Evidence URL</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Classification Signal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Discovery Source</t>
         </is>
@@ -535,40 +559,50 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://abatiboutique.online/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abaya, عباية, قميص, ملابس</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -600,40 +634,50 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>https://abayalabkw.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abaya, بشت, بنطلون, تنورة, جاكيت, عبايات</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -665,40 +709,50 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>https://abreezabaya.com/</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>homepage nav: abayas</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -726,42 +780,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>72</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://www.adidas.com.kw/</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -791,42 +856,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>1006</v>
+      </c>
+      <c r="G6" t="n">
+        <v>985</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://en-kw.aivi.com/</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t xml:space="preserve">homepage nav: </t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -856,42 +932,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>701</v>
+      </c>
+      <c r="G7" t="n">
+        <v>74</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://alaseel.com.kw/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: بناطيل, بيجامات, جاكيت, دراعة, فساتين, فستان</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -921,42 +1008,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>109386</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2508</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>https://alnasser.net/</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>homepage nav: apparel, blouse, cardigan, dress, hoodies, jacket</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -986,42 +1084,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>1096</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>https://alwareefkw.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: عبايه</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1053,40 +1162,50 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>https://www.alhazeemfashion.com.kw/</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>homepage nav: fashion, shemagh</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1116,42 +1235,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>45</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>https://abayaislamiya.com/</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1183,40 +1313,50 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>https://almohrastyle.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: blouse, pants, عبايات</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1246,42 +1386,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>7982</v>
+      </c>
+      <c r="G13" t="n">
+        <v>107</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>https://www.aloyoga.com/en-kw</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1313,40 +1464,50 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Verified - live re-check (KWD prices / cart on Kuwait storefront)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>https://ambroseabayas.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abaya, abayas, blazer, modest</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1374,42 +1535,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>25592</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250330043324/https://www.americaneagle.com.kw/en/buy-ae-ruffle-shirt-midi-dress-green.html</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1441,40 +1613,50 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Zid</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>https://arashastore.com/</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>homepage nav: ازياء, بلوزة, تنورة, جلابيات, جلابية, طقم</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1504,42 +1686,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>949</v>
+      </c>
+      <c r="G17" t="n">
+        <v>122</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>https://athleta.com.kw/</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>homepage nav: clothing, dresses, hoodies, jackets, jumpsuits, leggings</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1571,40 +1764,50 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>https://aysunkw.com/</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>homepage nav: coats, pants, shirt, shirts</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1636,40 +1839,50 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>https://b2lglam.com/</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>homepage nav: عبايتج</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1699,42 +1912,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>2474</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1006</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>https://www.balenciaga.com/en-kw</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -1764,42 +1988,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>187</v>
+      </c>
+      <c r="G21" t="n">
+        <v>198</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>https://www.bananarepublic.com.kw/</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>homepage nav: blazer, blazers, blouses, clothing, coats, denim</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1827,42 +2062,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>12030</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1227</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>https://www.bershka.com/kw/ar/%D9%86%D8%B3%D8%A7%D8%A1/shoes-c1010838068.html</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1894,40 +2140,50 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>https://kw.p3ly.com/</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>homepage nav: أزياء, لانجري, ملابس</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -1957,42 +2213,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>617</v>
+      </c>
+      <c r="G24" t="n">
+        <v>302</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>https://www.blackwhitekw.com/</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>homepage nav: بناطيل, طقم, فساتين, قمصان, ملابس</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2022,42 +2289,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>996</v>
+      </c>
+      <c r="G25" t="n">
+        <v>936</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>https://www.blinktrends.com.kw/</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2087,42 +2365,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>102347</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16964</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>https://bloomingdales.com.kw/</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>homepage nav: أزياء</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2154,40 +2443,50 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>https://bluestoreq8.com/</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>homepage nav: أزياء</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2217,42 +2516,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>4157</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1392</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>https://www.bottegaveneta.com/en-kw</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2282,42 +2592,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>15528</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2952</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>https://www.brandsforless.com/en-kw</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2347,42 +2668,58 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>340</v>
+      </c>
+      <c r="G30" t="n">
+        <v>52</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Root-domain figure (burberry.com) - includes global/other-country traffic</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Verified - live re-check (KWD prices / cart on Kuwait storefront)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>https://kw.burberry.com/</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>homepage nav: activewear, blazers, clothes, coats, denim, dresses</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2410,42 +2747,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>https://cabanakw.com/</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>homepage nav: dresses, polo shirts, shirts, shorts, skirts, swimwear</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2473,42 +2821,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>7039</v>
+      </c>
+      <c r="G32" t="n">
+        <v>857</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>https://www.calvinklein.com.kw/</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2538,42 +2897,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>159290</v>
+      </c>
+      <c r="G33" t="n">
+        <v>18269</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20261011132057/https://www.centrepointstores.com/sa/ar/buy-amla-baby-remote-control-swing-system-car/p/169778248?gbraid=0AAAAACwAzs3EdPrFuSSMNm0l0Slgun4BB&amp;gad_source=5&amp;gad_campaignid=22918204761&amp;gclid=EAIaIQobChMI8P_4gYaylwMVYsdPCB0syjznEAEYASABEgIwC_D_BwE</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2605,40 +2975,50 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>https://chickuwait.com/</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2668,42 +3048,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>4894</v>
+      </c>
+      <c r="G35" t="n">
+        <v>617</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>https://kw.cos.com/en/</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>homepage nav: clothing, fashion</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2735,40 +3126,50 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>https://darraferoz.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: abayas, activewear, dress, dresses</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -2798,42 +3199,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>20427</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1241</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>https://decathlon.com.kw/</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>directory category 'Sports, Fitness &amp; Outdoor' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2863,42 +3275,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>141</v>
+      </c>
+      <c r="G38" t="n">
+        <v>31</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>https://www.desigual.com/en_KW/</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>directory category 'Pets' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2928,42 +3351,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>510</v>
+      </c>
+      <c r="G39" t="n">
+        <v>191</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>https://kw.diesel.com/</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -2993,42 +3427,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>4573</v>
+      </c>
+      <c r="G40" t="n">
+        <v>485</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251012213912/https://dkny.com.kw/ar/collections/fp-shoes/products/kw356902blk</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3058,42 +3503,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>6193</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1232</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Verified - live re-check (KWD prices / cart on Kuwait storefront)</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>https://www.dolcegabbana.com/en-kw/</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Kuwait-locale storefront (/en-kw, KWD) with clothing nav; homepage nav fetched during locale probe</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3125,40 +3581,50 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>https://elitewholesalekuwait.com/</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>homepage nav: abaya</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3188,42 +3654,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>https://ar-kw.emvano.com/</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>homepage nav: بناطيل, فساتين, قمصان, ملابس</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3255,40 +3732,50 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>https://www.etedalalhmaidi.com/kw/</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>directory category 'Flowers, Gifts &amp; Party' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3318,42 +3805,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>924</v>
+      </c>
+      <c r="G45" t="n">
+        <v>96</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260422015803/https://falke.com.kw/products/men-long-sleeve-shirt-maximum-warm-33523_7385</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3381,42 +3879,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>38192</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3629</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>https://www.footlocker.com.kw/en/</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t xml:space="preserve">homepage nav: </t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3446,42 +3955,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>2335</v>
+      </c>
+      <c r="G47" t="n">
+        <v>148</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>https://gant.com.kw/</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3511,42 +4031,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>6125</v>
+      </c>
+      <c r="G48" t="n">
+        <v>587</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>https://www.gap.com.kw/</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>homepage nav: clothing, denim, dress, dresses, hoodie, jacket</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3578,40 +4109,50 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>https://www.giordano.com.kw/</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3641,42 +4182,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>9631</v>
+      </c>
+      <c r="G50" t="n">
+        <v>406</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>https://www.gymshark.com.kw/</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>homepage nav: بناطيل, ملابس</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3704,42 +4256,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>65348</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6409</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>https://kw.hm.com/ar/buy-2-pack-make-sponges-pink-purple</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3767,42 +4330,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>17452</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3599</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>https://www.harveynichols.com.kw/en/</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>homepage nav: fashion</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3832,42 +4406,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>93</v>
+      </c>
+      <c r="G53" t="n">
+        <v>45</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Zid</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>https://hawraaabaya.com/</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>homepage nav: تنورة, حجاب, طقم, عبايات</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -3895,42 +4480,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="n">
+        <v>3016</v>
+      </c>
+      <c r="G54" t="n">
+        <v>448</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260211012338/https://www.hugoboss.com/kw/en/cotton-jersey-t-shirt-with-stripe-and-logo/4063548594390.html</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -3960,42 +4556,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>42212</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2138</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>https://www.intersport.com.kw/</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>homepage nav: clothing, hoodies, jackets, swimwear, underwear</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4027,40 +4634,50 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>https://justladykw.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: فساتين</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4090,42 +4707,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="n">
+        <v>136</v>
+      </c>
+      <c r="G57" t="n">
+        <v>42</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>https://kiabi.kw/</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4157,40 +4785,55 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>https://ku-market.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: activewear, blouses, clothing, coats, dresses, jackets</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4220,42 +4863,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>107</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>https://www.kuwaitboutique.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: clothes, hoodie, hoodies</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4283,42 +4937,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>https://www.lasenzakuwait.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: lingerie, pants, shorts, underwear</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4350,40 +5015,50 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>https://lab.com.kw/</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4411,42 +5086,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>182</v>
+      </c>
+      <c r="G62" t="n">
+        <v>14</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>https://www.lacoste.ae/</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>homepage nav: clothing, coats, dresses, fashion, jackets, loungewear</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4476,40 +5162,55 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>https://www.lcwaikiki.com.kw/</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4537,42 +5238,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="n">
+        <v>63</v>
+      </c>
+      <c r="G64" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>https://www.lifestyleshops.com/kw/en</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4604,40 +5316,50 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>https://listroma.com/</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>homepage nav: أزياء</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -4667,42 +5389,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="n">
+        <v>252768</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34734</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20261004041456/https://gcc.luluhypermarket.com/en-kw/bee-polypropylene-lunch-box-with-spoon-fork-set-782/p/2433012/</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4734,40 +5467,50 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>https://lulwamoda.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: عبايات</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4797,42 +5540,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="n">
+        <v>1631</v>
+      </c>
+      <c r="G68" t="n">
+        <v>251</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>https://www.maje.com.kw/</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>homepage nav: blazers, cardigan, cardigans, denim, dress, dresses</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4860,42 +5614,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>15592</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1556</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>https://shop.mango.com/kw/en/p/kids/baby-girls/sweatshirts/hello-kitty-sweatshirt/37073306/43/00</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4925,42 +5690,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>https://www.marksandspencer.com.kw/en/fashion</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>homepage nav: fashion, jackets, lingerie, nightwear, shirts, skirts</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -4988,42 +5764,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>7537</v>
+      </c>
+      <c r="G71" t="n">
+        <v>319</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>https://www.massimodutti.com/kw/runway/runway-fw25-w</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5051,42 +5838,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="n">
+        <v>49958</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4967</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251022035748/https://www.maxfashion.com/kw/ar/buy-beaded-layered-necklace-with-lobster-clasp-closure/p/165457961</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5118,40 +5916,50 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>https://melissia.com.kw/ar/</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>homepage nav: abaya</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5181,42 +5989,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="n">
+        <v>2399</v>
+      </c>
+      <c r="G74" t="n">
+        <v>500</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>SFCC</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>https://www.michaelkors.com.kw/</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>homepage nav: clothing, dresses, jackets</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5244,42 +6063,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="n">
+        <v>8229</v>
+      </c>
+      <c r="G75" t="n">
+        <v>808</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>https://www.miumiu.com/kw/</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5309,42 +6139,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G76" t="n">
+        <v>45</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>https://modish.com.kw/</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>homepage nav: blazers, cardigans, coats, denim, dresses, hijab</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5372,42 +6213,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G77" t="n">
+        <v>265</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>https://www.moncler.com/en-kw/</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -5439,40 +6291,50 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>https://mrmr.com.kw/</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>homepage nav: fashion, دراعة, فستان</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5500,42 +6362,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="n">
+        <v>17475</v>
+      </c>
+      <c r="G79" t="n">
+        <v>9473</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>https://www.namshi.com/kuwait-ar/buy-ecotools-360-ultimate-sheer-foundation-brush/ZCCFCFFE879C5D3A8C0D0Z/p/</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5567,40 +6440,50 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>https://nayra.style/</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5630,42 +6513,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="n">
+        <v>9540</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1143</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>https://www.newbalance.com.kw/en/</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t xml:space="preserve">homepage nav: </t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5693,42 +6587,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="n">
+        <v>17556</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5801</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>https://www.nextdirect.com/kw/</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5758,42 +6663,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="n">
+        <v>35021</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2524</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>https://www.nike.com.kw/en/home/</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>homepage nav: clothing, hoodies, jackets, shorts, sportswear, sweatshirts</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5825,40 +6741,50 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>https://oosha.store/</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>homepage nav: jacket</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -5888,42 +6814,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="n">
+        <v>25979</v>
+      </c>
+      <c r="G85" t="n">
+        <v>6739</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>https://kuwait.ounass.com/</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>homepage nav: clothing</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -5951,42 +6888,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="n">
+        <v>8586</v>
+      </c>
+      <c r="G86" t="n">
+        <v>791</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>https://www.oysho.com/kw/%D8%A7%D9%95%D8%B7%D9%84%D8%A7%D9%84%D8%A9-%D9%83%D8%A7%D9%85%D9%84%D8%A9-compressive-%D8%B4%D9%88%D8%B1%D8%AA-%D8%B3%D9%88%D8%AF%D8%A7%D8%A1-l30349206800BSBS</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6014,42 +6962,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" t="n">
+        <v>6936</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1926</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>https://www.prada.com/kw/</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6077,42 +7036,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" t="n">
+        <v>6486</v>
+      </c>
+      <c r="G88" t="n">
+        <v>694</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>https://www.pullandbear.com/kw/%D8%AC%D9%8A%D9%86%D8%B2-%D9%81%D8%B6%D9%81%D8%A7%D8%B6-%D8%A8%D9%82%D8%B5%D8%A9-%D8%A8%D8%A7%D9%84%D9%88%D9%86-%D9%88%D8%A8%D9%84%D9%8A%D8%B3%D9%8A%D9%87-l07662409</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6142,42 +7112,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" t="n">
+        <v>8676</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1026</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>https://www.rivafashion.com/en-kw/</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6209,40 +7190,50 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>https://sstylekw.com/</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>homepage nav: dress, ready to wear</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -6272,42 +7263,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" t="n">
+        <v>2335</v>
+      </c>
+      <c r="G91" t="n">
+        <v>211</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251018070132/https://www.sandro.com.kw/ar/products/sface00434-slim-leather-belt-brown</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6337,42 +7339,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" t="n">
+        <v>547</v>
+      </c>
+      <c r="G92" t="n">
+        <v>49</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>https://shadow.com.kw/</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>homepage nav: abaya, abayas, blazer</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6400,42 +7413,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="n">
+        <v>23248</v>
+      </c>
+      <c r="G93" t="n">
+        <v>175</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>https://us.shein.com/?cdn_rsite=cf&amp;ref=www&amp;rep=dir&amp;ret=us</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>homepage nav: clothing, fashion</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6467,40 +7491,50 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>https://sj-abaya.com/ar-kw/</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6530,42 +7564,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" t="n">
+        <v>26</v>
+      </c>
+      <c r="G95" t="n">
+        <v>68</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>https://sleepwearkuwait.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: dress, loungewear, pajama, shirts</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6595,42 +7640,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" t="n">
+        <v>7040</v>
+      </c>
+      <c r="G96" t="n">
+        <v>610</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>https://www.snkr.com.kw/</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>homepage nav: apparel</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6662,40 +7718,50 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>https://souqsara.com.kw/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: بنطلون, تنورة, جاكيت, حجاب, طقم, عباية</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6727,40 +7793,50 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>https://specialabayakw.com/</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Abayas &amp; Modest' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6788,42 +7864,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" t="n">
+        <v>6018</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1629</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250524064006/https://www.splashfashions.com/kw/ar/%D8%A7%D9%83%D8%B3%D8%B3%D9%88%D8%A7%D8%B1%D8%A7%D8%AA/%D8%A7%D9%84%D9%86%D8%B3%D8%A7%D8%A1/%D8%AD%D9%82%D8%A7%D8%A6%D8%A8-%D9%8A%D8%AF-%D9%86%D8%B3%D8%A7%D8%A6%D9%8A%D8%A9/%D8%B4%D9%88%D9%85%D8%A7%D8%B1%D8%AA-%D8%B4%D9%86%D8%B7%D8%A9-%D8%AA%D9%88%D8%AA-%D9%83%D8%AA%D9%84-%D9%85%D9%84%D9%88%D9%91%D9%86%D8%A9-%D9%88%D8%B3%D8%AD%D9%91%D8%A7%D8%A8-%D8%A5%D8%BA%D9%84%D8%A7%D9%82-%D9%88%D9%85%D9%82%D8%A8%D8%B6-%D9%85%D8%B2%D8%AF%D9%88%D8%AC-%D9%85%D9%86-%D9%85%D9%8A%D8%B3%D9%8A/p/c/cpwomen</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6853,42 +7940,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" t="n">
+        <v>1429</v>
+      </c>
+      <c r="G100" t="n">
+        <v>233</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>https://squatwolf.com/en-kw/products/qtr-zip-untamed-top-surf-spray-print</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -6916,42 +8014,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" t="n">
+        <v>6650</v>
+      </c>
+      <c r="G101" t="n">
+        <v>407</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>https://www.stradivarius.com/kw/en/</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -6981,42 +8090,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" t="n">
+        <v>3227</v>
+      </c>
+      <c r="G102" t="n">
+        <v>5569</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>https://stylishop.com/kw/en</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -7046,42 +8166,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" t="n">
+        <v>43994</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3306</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>https://en-kw.sssports.com/</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>homepage nav: clothing, dresses, hijab, hoodies, jackets, leggings</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7111,42 +8242,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G104" t="n">
+        <v>557</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>https://www.tedbaker.kw/</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7176,42 +8318,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" t="n">
+        <v>25774</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1391</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>https://www.theathletesfoot.com.kw/</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>homepage nav: apparel, dresses, hoodies, jackets, leggings, pants</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7241,42 +8394,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" t="n">
+        <v>480</v>
+      </c>
+      <c r="G106" t="n">
+        <v>715</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>https://theonekdshop.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>WooCommerce store API categories: activewear, blazers, cardigans, clothes, clothing, dresses</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7306,42 +8470,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G107" t="n">
+        <v>231</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>https://thoubi.com/</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="P107" t="inlineStr">
         <is>
           <t>directory category 'Fashion - Men' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -7371,42 +8546,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" t="n">
+        <v>4536</v>
+      </c>
+      <c r="G108" t="n">
+        <v>431</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>https://www.toryburch.com.kw/</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="P108" t="inlineStr">
         <is>
           <t>homepage nav: clothing, denim, فساتين, قفطان, قمصان, ملابس</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr">
+      <c r="Q108" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7438,40 +8624,50 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251111021404/https://triumph.com.kw/ar/collections/sloggi_women_knickers_string-thongs/products/10214636-6308</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="P109" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7501,42 +8697,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" t="n">
+        <v>3948</v>
+      </c>
+      <c r="G110" t="n">
+        <v>194</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>https://www.uspoloassn.com.kw/</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>directory category 'Fashion &amp; Apparel' + brand/brand-page knowledge (homepage not fetchable)</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7566,42 +8773,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" t="n">
+        <v>4423</v>
+      </c>
+      <c r="G111" t="n">
+        <v>794</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712150340/https://www.valentino.com/en-kw/men/shoes/loafers-and-driver?pagination=2</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7629,42 +8847,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="n">
+        <v>3228</v>
+      </c>
+      <c r="G112" t="n">
+        <v>256</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>https://www.versace.com/kw/en/</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="P112" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -7694,42 +8923,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" t="n">
+        <v>15917</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1870</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>https://www.victoriassecret.com.kw/en/</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="P113" t="inlineStr">
         <is>
           <t>homepage nav: lingerie</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7759,42 +8999,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" t="n">
+        <v>8247</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2475</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t>Known major retailer - manually accepted</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>https://www.vogacloset.com/kw</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -7826,40 +9077,50 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>Magento / custom (not confirmed)</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>https://wsfabaya.com/</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="P115" t="inlineStr">
         <is>
           <t>homepage nav: abaya, abayas, blazers, dress, fashion, modest</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -7891,40 +9152,50 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t>Unverified - fashion-confirmed; weak Kuwait/e-commerce signal</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>https://wynwoodkw.com/</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="P116" t="inlineStr">
         <is>
           <t>homepage nav: hoodies, shirts, shorts, tshirts</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="Q116" t="inlineStr">
         <is>
           <t>New discovery</t>
         </is>
@@ -7952,42 +9223,53 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" t="n">
+        <v>52625</v>
+      </c>
+      <c r="G117" t="n">
+        <v>3329</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>Not detected (bot-walled/rate-limited)</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>Major (intl/regional chain)</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t>Verified (secondary evidence: Common Crawl/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>https://www.zara.com/kw/ar/monsters-l18726.html</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="P117" t="inlineStr">
         <is>
           <t>known major fashion retailer; Kuwait storefront evidence from verifier (CC/Wayback KWD product page)</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="Q117" t="inlineStr">
         <is>
           <t>Existing research</t>
         </is>
@@ -8019,40 +9301,50 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="N118" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t>https://activeleia.com/products/zipper-jacket-set</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="P118" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8082,42 +9374,53 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t>https://aidanglobal.com/product/premium-racefit-cycling-jersey-corex/</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="P119" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8149,40 +9452,50 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="N120" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>https://aurelliaofficial.com/products/caramel-sweater-dark-chocolate-leather-skirt</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="P120" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="Q120" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8214,40 +9527,50 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>OpenCart</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>https://blacklinewear.com/</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="P121" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="Q121" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8279,40 +9602,50 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>Women, Men</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>Not detected</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="O122" t="inlineStr">
         <is>
           <t>https://doekw.com/en/products/4/men-clothing</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="P122" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
+      <c r="Q122" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8344,40 +9677,50 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="N123" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="O123" t="inlineStr">
         <is>
           <t>https://hamemdesign.com/products/عباة-ميلا-بني-أو-أسود</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="P123" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="Q123" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8409,40 +9752,50 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>Small / local brand</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="N124" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="O124" t="inlineStr">
         <is>
           <t>https://maisonrkw.com/</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="P124" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="Q124" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -8472,42 +9825,53 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" t="n">
+        <v>106</v>
+      </c>
+      <c r="G125" t="n">
+        <v>32</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>nopCommerce</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>https://shopflain.com/pants-3</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="P125" t="inlineStr">
         <is>
           <t>homepage/nav clothing keywords (StoreLeads gap fill)</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="Q125" t="inlineStr">
         <is>
           <t>StoreLeads gap fill</t>
         </is>
@@ -29818,7 +31182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -30491,10 +31855,146 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66" ht="150" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Organic traffic (Semrush)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Filled with traffic</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Not checked (other)</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>% of rows with a Semrush answer (traffic + no data)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>70.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Rows with root-domain note (Semrush reported the parent root domain)</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Rows flagged as test/placeholder store (not deleted)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Direct Semrush lookups for this file (domain_rank, MCP)</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Semrush organic traffic and keywords, database kw (batch results plus direct domain_rank lookups for domains missing from the batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Selection rule</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Checked when Website Pages Count is blank/non-numeric or &gt; 500; 500 pages or fewer are labelled 'Not checked (&lt;=500 pages)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Check date</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
